--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +772,442 @@
         <is>
           <t>Odd_Corners_Under115</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>8266448</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>45947.20833333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>['55', '65']</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8266446</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>45947.29513888889</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP3"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1208,224 @@
       </c>
       <c r="BP3" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8266505</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>45948.125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Melbourne City FC</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP4"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,6 +1425,442 @@
         <v>2.28</v>
       </c>
       <c r="BP4" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8266447</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45948.23263888889</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8266504</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>45948.32291666666</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>['16', '26']</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>['45+3', '69']</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP6" t="n">
         <v>1.44</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1862,6 +1862,224 @@
       </c>
       <c r="BP6" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8266506</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45949.04166666666</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>['28', '30', '90+8']</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>['14', '80']</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,6 +2080,224 @@
       </c>
       <c r="BP7" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8266468</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45954.23263888889</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>['14', '20', '45+2', '79', '90+1']</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>['25', '55']</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2298,6 +2298,442 @@
       </c>
       <c r="BP8" t="n">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8266469</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45955.04166666666</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8266507</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>45955.125</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Melbourne City FC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>['5', '36', '84', '90+1']</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2734,6 +2734,224 @@
       </c>
       <c r="BP10" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8266471</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45955.23263888889</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>['58', '90']</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2952,6 +2952,224 @@
       </c>
       <c r="BP11" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8266470</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>45955.95833333334</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>['76', '90+6']</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP12"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3170,6 +3170,224 @@
       </c>
       <c r="BP12" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8266472</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>45957.20833333334</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>['11', '64']</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -3330,13 +3330,13 @@
         <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3388,6 +3388,442 @@
       </c>
       <c r="BP13" t="n">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8266510</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>45961.23263888889</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Melbourne City FC</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8266473</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45961.32291666666</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>['11', '54']</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.5</v>
@@ -3824,6 +3824,442 @@
       </c>
       <c r="BP15" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8266475</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45962.04166666666</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>['25', '79']</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8266478</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>45962.125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>['11', '51', '58', '74']</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP17"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -4260,6 +4260,224 @@
       </c>
       <c r="BP17" t="n">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8266479</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>45962.23263888889</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -4478,6 +4478,224 @@
       </c>
       <c r="BP18" t="n">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8266508</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45963.125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR18" t="n">
         <v>1.75</v>
@@ -4696,6 +4696,224 @@
       </c>
       <c r="BP19" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8266509</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>45968.23263888889</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>['63', '68']</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP20"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2876,7 +2876,7 @@
         <v>3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.5</v>
@@ -4914,6 +4914,224 @@
       </c>
       <c r="BP20" t="n">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8266480</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45968.32291666666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -4859,13 +4859,13 @@
         <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
         <v>13</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BP22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -5132,6 +5132,224 @@
       </c>
       <c r="BP21" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8266481</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45969.125</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>['1', '34']</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP22"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>2</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AR14" t="n">
         <v>0.8100000000000001</v>
@@ -5350,6 +5350,224 @@
       </c>
       <c r="BP22" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8266483</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45969.23263888889</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Melbourne City FC</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>['2', '55']</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X23" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP23"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.67</v>
@@ -5568,6 +5568,442 @@
       </c>
       <c r="BP23" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8266482</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>45970.04166666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>['76', '90+3']</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8266474</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45970.125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['31', '79', '89']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR14" t="n">
         <v>0.8100000000000001</v>
@@ -5492,7 +5492,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AR23" t="n">
         <v>1.1</v>
@@ -6004,6 +6004,224 @@
       </c>
       <c r="BP25" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8266484</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>45982.23263888889</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Melbourne City FC</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>['12', '15', '79', '84']</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -5710,7 +5710,7 @@
         <v>3</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>2.31</v>
@@ -6222,6 +6222,224 @@
       </c>
       <c r="BP26" t="n">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8266485</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45983.04166666666</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X27" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BP28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.25</v>
@@ -2876,7 +2876,7 @@
         <v>3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
         <v>1.35</v>
@@ -6440,6 +6440,224 @@
       </c>
       <c r="BP27" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8266511</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45983.125</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>['1', '11', '23']</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>['9', '39']</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP28"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>1.27</v>
@@ -6658,6 +6658,224 @@
       </c>
       <c r="BP28" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8266488</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>45983.23263888889</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>['58', '70', '76']</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.33</v>
@@ -2658,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.5</v>
@@ -6600,13 +6600,13 @@
         <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX28" t="n">
         <v>4</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>8</v>
@@ -6821,13 +6821,13 @@
         <v>12</v>
       </c>
       <c r="AX29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
         <v>6</v>
@@ -6875,6 +6875,442 @@
         <v>2.4</v>
       </c>
       <c r="BP29" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8270570</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>45983.95833333334</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8266513</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>45984.125</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>['38', '79']</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BP31" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.25</v>
@@ -3748,7 +3748,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR15" t="n">
         <v>1.27</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR29" t="n">
         <v>2.16</v>
@@ -7312,6 +7312,224 @@
       </c>
       <c r="BP31" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8266512</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>45989.23263888889</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Brisbane Roar</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP32"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.5</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>1</v>
@@ -7530,6 +7530,224 @@
       </c>
       <c r="BP32" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8266476</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>45990.04166666666</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>['13', '52']</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP33"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR14" t="n">
         <v>0.8100000000000001</v>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR23" t="n">
         <v>1.1</v>
@@ -6146,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR26" t="n">
         <v>1.6</v>
@@ -7748,6 +7748,224 @@
       </c>
       <c r="BP33" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8266449</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>45990.125</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Central Coast Mariners</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Melbourne City FC</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BP37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.2</v>
@@ -2004,7 +2004,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.33</v>
@@ -2658,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
         <v>2.16</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.33</v>
@@ -5928,7 +5928,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR25" t="n">
         <v>0.98</v>
@@ -6579,7 +6579,7 @@
         <v>1.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ28" t="n">
         <v>1</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.5</v>
@@ -7236,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR31" t="n">
         <v>1.8</v>
@@ -7966,6 +7966,660 @@
       </c>
       <c r="BP34" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8266486</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>45990.23263888889</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8266514</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>45990.95833333334</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>['3', '41']</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8266450</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>45991.16666666666</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>['66', '88']</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP37"/>
+  <dimension ref="A1:BP39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR15" t="n">
         <v>1.27</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR18" t="n">
         <v>1.75</v>
@@ -4838,7 +4838,7 @@
         <v>3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR20" t="n">
         <v>1.51</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ21" t="n">
         <v>1</v>
@@ -6800,7 +6800,7 @@
         <v>3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR29" t="n">
         <v>2.16</v>
@@ -7454,7 +7454,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR32" t="n">
         <v>1.15</v>
@@ -8541,7 +8541,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37" t="n">
         <v>2</v>
@@ -8620,6 +8620,442 @@
       </c>
       <c r="BP37" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8266451</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>45996.23263888889</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Melbourne Victory FC</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X38" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8266452</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>45996.32291666666</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Perth Glory FC</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP39"/>
+  <dimension ref="A1:BP40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.25</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR19" t="n">
         <v>1.44</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.5</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ36" t="n">
         <v>1</v>
@@ -9056,6 +9056,224 @@
       </c>
       <c r="BP39" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8266489</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>45997.04166666666</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>['7', '72', '80']</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X40" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP40"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.8</v>
@@ -3530,7 +3530,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR14" t="n">
         <v>0.8100000000000001</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ17" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
         <v>1.1</v>
@@ -6146,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
         <v>1.6</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ31" t="n">
         <v>2</v>
@@ -7890,7 +7890,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AR34" t="n">
         <v>1.22</v>
@@ -9274,6 +9274,224 @@
       </c>
       <c r="BP40" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8266453</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>45997.125</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Newcastle Jets FC</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Melbourne City FC</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>
